--- a/UTCUTS/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
+++ b/UTCUTS/A2_Extra_Inputs/A-Xtra_Emissions.xlsx
@@ -5076,5 +5076,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55B0E789-E3F9-4F5A-A59D-82B118AA528E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2C44425-E9A6-4650-899D-0E35E170E7C1}"/>
 </file>